--- a/output/pdf_financials_xlsx/AGAG.xlsx
+++ b/output/pdf_financials_xlsx/AGAG.xlsx
@@ -1047,13 +1047,13 @@
         <v>0.001865</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.01197</v>
+        <v>-0.01197</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.077</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.436</v>
       </c>
     </row>
     <row r="13">
@@ -1951,13 +1951,13 @@
         <v>-0.40033</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.426532</v>
+        <v>-0.402592</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.143</v>
+        <v>-3.066</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-14.399</v>
+        <v>-13.963</v>
       </c>
     </row>
     <row r="28">
@@ -2063,13 +2063,13 @@
         <v>-0.40033</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.426532</v>
+        <v>-0.402592</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.121</v>
+        <v>-3.044</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-14.266</v>
+        <v>-13.83</v>
       </c>
     </row>
     <row r="30">
@@ -2318,19 +2318,19 @@
         <v>0.031671</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.04052</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01516</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.146925</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>22.384</v>
       </c>
     </row>
     <row r="35">
@@ -2426,19 +2426,19 @@
         <v>0.031671</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.04052</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.01516</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.146925</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>22.384</v>
       </c>
     </row>
     <row r="37">
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.11451</v>
+        <v>0.09934999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.2513</v>
+        <v>0.104375</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.273999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>23.627</v>
+        <v>1.243</v>
       </c>
     </row>
     <row r="49">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8867,7 +8867,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10491,7 +10495,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11134,7 +11142,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11682,7 +11694,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11866,7 +11878,11 @@
           <t>Reclamation deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -19887,7 +19903,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -21015,7 +21031,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -22873,7 +22889,11 @@
           <t>Interest earned on reclamation deposits</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -25350,7 +25370,11 @@
           <t>Interest earned on reclamation deposits</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -26899,7 +26923,11 @@
           <t>Interest earned on reclamation deposits</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -31697,11 +31725,7 @@
           <t>General and administration expense (Note 13)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32874,7 +32898,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -34235,7 +34259,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">

--- a/output/pdf_financials_xlsx/AGAG.xlsx
+++ b/output/pdf_financials_xlsx/AGAG.xlsx
@@ -1068,25 +1068,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.008062</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.235152</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.33516</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.337216</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.369944</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>0.357502</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0.352212</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>-0</v>
@@ -1916,25 +1916,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.924105</v>
+        <v>-0.932167</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.474234</v>
+        <v>-3.709386</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.895443</v>
+        <v>-2.230603</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.995311</v>
+        <v>-2.332527</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.621344</v>
+        <v>-5.991288</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.121134</v>
+        <v>-2.478636</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.672742</v>
+        <v>-1.024954</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.350489</v>
@@ -2028,25 +2028,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.923448</v>
+        <v>-0.9315099999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.469014</v>
+        <v>-3.704166</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.895443</v>
+        <v>-2.230603</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.995311</v>
+        <v>-2.332527</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.621344</v>
+        <v>-5.991288</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.121134</v>
+        <v>-2.478636</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.672742</v>
+        <v>-1.024954</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.350489</v>
@@ -2094,19 +2094,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-884.8238001652529</v>
+        <v>-1041.281971085395</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-389.1019678275504</v>
+        <v>-454.8618464544588</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1925.605804210656</v>
+        <v>-2052.331070202723</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-11570.03218240332</v>
+        <v>-13520.07854688267</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-6953.405684754522</v>
+        <v>-10593.83979328166</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -39963,7 +39963,11 @@
           <t>Net finance expenses $</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
